--- a/ct/tests/fixtures/repository_cutover/workspace/excel/UIConfig.xlsx
+++ b/ct/tests/fixtures/repository_cutover/workspace/excel/UIConfig.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +26,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <name val="Aptos"/>
+      <color rgb="00334155"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -47,24 +40,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C9A227"/>
-        <bgColor rgb="00C9A227"/>
+        <fgColor rgb="0092400E"/>
+        <bgColor rgb="0092400E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4332"/>
-        <bgColor rgb="001B4332"/>
+        <fgColor rgb="00334155"/>
+        <bgColor rgb="00334155"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -78,57 +71,116 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EDF7EE"/>
-          <bgColor rgb="00EDF7EE"/>
+          <fgColor rgb="00F8FAFC"/>
+          <bgColor rgb="00F8FAFC"/>
         </patternFill>
       </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00CCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="00CCCCCC"/>
-        </right>
-      </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="00581C87"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-          <bgColor rgb="00FFFFFF"/>
+          <fgColor rgb="00F3E8FF"/>
         </patternFill>
       </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00CCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="00CCCCCC"/>
-        </right>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00475569"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F1F5F9"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -201,6 +253,25 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ct</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>类型：UIConfigLayer；UI 层级
+Page: 页面
+Modal: 模态
+Panel: 面板
+Overlay: 覆盖层</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,62 +573,62 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>界面唯一 ID（行主键，禁止修改；Config Lua 生成时从本表读取）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>UI 层级：Page 全屏页栈 / Modal 弹窗栈 / Panel 常驻面板 / Overlay 浮层</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Addressables 资源 key（prefab 路径）</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Overlay 专用：是否拦截输入（Toast 透传 / Loading 拦截），其他层忽略</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Page 专用：是否入历史栈</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Id
 int32</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Layer
-enum[Page,Modal,Panel,Overlay]</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+UIConfigLayer</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>ResourceKey
 string</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>BlocksRaycast
 bool</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Stack
 bool</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>界面唯一 ID（行主键，禁止修改；Config Lua 生成时从本表读取）</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>UI 层级：Page 全屏页栈 / Modal 弹窗栈 / Panel 常驻面板 / Overlay 浮层</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Addressables 资源 key（prefab 路径）</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Overlay 专用：是否拦截输入（Toast 透传 / Loading 拦截），其他层忽略</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Page 专用：是否入历史栈</t>
         </is>
       </c>
     </row>
@@ -688,19 +759,53 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:E1000">
+  <conditionalFormatting sqref="A3:A1048576">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>MOD(ROW(),2)=1</formula>
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="B3:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="B3:B1048576">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>B3&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C1048576">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D1048576">
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>D3=TRUE</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>D3=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E1048576">
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E3=TRUE</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="3">
+      <formula>E3=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="A3:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="B3:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Page,Modal,Panel,Overlay"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>